--- a/data/lexicon_review/Egyptian.xlsx
+++ b/data/lexicon_review/Egyptian.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
@@ -864,14 +864,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2ntima2</t>
+          <t>entima2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
@@ -983,14 +983,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>intima2</t>
+          <t>entema2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1102,14 +1102,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>entima2</t>
+          <t>intima2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
@@ -1194,17 +1194,17 @@
           <t>ت</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
           <t>ا</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>ء</t>
@@ -1221,14 +1221,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>entema2</t>
+          <t>2ntmaa2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>m</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>a</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1313,17 +1313,17 @@
           <t>ت</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>ء</t>
@@ -1340,7 +1340,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2ntmaa2</t>
+          <t>2ntima2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>m</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>intimaa2</t>
+          <t>entemaa2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1582,14 +1582,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>entemaa2</t>
+          <t>intimaa2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
@@ -2307,14 +2307,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>goz2</t>
+          <t>joz2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>j</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
@@ -2402,14 +2402,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>joz2</t>
+          <t>goz2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>j</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2798,7 +2798,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>la2em</t>
+          <t>la2ym</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>y</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
@@ -2872,22 +2872,22 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
         <is>
           <t>ئ</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>l2eem</t>
+          <t>la2em</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2913,20 +2913,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>ee</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -2963,7 +2967,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
@@ -2971,22 +2975,22 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ئ</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ئ</t>
+          <t>ي</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
           <t>م</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3000,7 +3004,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>la2ym</t>
+          <t>l2eem</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3012,24 +3016,20 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ee</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
           <t>m</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
@@ -3420,14 +3420,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2st3mal</t>
+          <t>est3mal</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
@@ -3543,14 +3543,14 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>est3mal</t>
+          <t>2st3mal</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
@@ -3666,14 +3666,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>isti3mal</t>
+          <t>este3mal</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
@@ -3793,14 +3793,14 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>este3mal</t>
+          <t>isti3mal</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
@@ -5265,14 +5265,14 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7oma</t>
+          <t>homa</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
@@ -5455,14 +5455,14 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>homa</t>
+          <t>7oma</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
@@ -5550,14 +5550,14 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>7omma</t>
+          <t>homma</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5612,7 +5612,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
@@ -5645,14 +5645,14 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>homma</t>
+          <t>7omma</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
@@ -6243,7 +6243,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>barkyh</t>
+          <t>barkeh</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>e</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -6358,7 +6358,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>barkih</t>
+          <t>barkyh</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
@@ -6473,14 +6473,14 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>barkeh</t>
+          <t>parkeh</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>p</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
@@ -6588,14 +6588,14 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>parkeh</t>
+          <t>barkih</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -6658,7 +6658,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
@@ -6681,12 +6681,12 @@
           <t>ك</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr">
+      <c r="H170" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>ه</t>
@@ -6703,14 +6703,14 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>parquet</t>
+          <t>barqueh</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6728,19 +6728,15 @@
           <t>q</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>eh</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -6892,7 +6888,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
@@ -6920,12 +6916,12 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr">
+      <c r="I176" t="inlineStr">
         <is>
           <t>ه</t>
         </is>
       </c>
+      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
@@ -6937,14 +6933,14 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>barqueh</t>
+          <t>parkeeh</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>p</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6959,20 +6955,20 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>q</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>ee</t>
+        </is>
+      </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>eh</t>
-        </is>
-      </c>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
@@ -7145,17 +7141,17 @@
           <t>ك</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="J182" t="inlineStr">
         <is>
           <t>ه</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
@@ -7167,7 +7163,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>parkeeh</t>
+          <t>parquet</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7189,20 +7185,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>q</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ee</t>
+          <t>u</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr"/>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
@@ -7352,39 +7352,15 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>ث</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>ن</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>ة</t>
-        </is>
-      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
@@ -7397,41 +7373,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>thanwya</t>
+          <t>thanawy</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>th</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
@@ -7467,15 +7419,39 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ث</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>ة</t>
+        </is>
+      </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
@@ -7488,17 +7464,41 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>thanawy</t>
+          <t>thanwya</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>th</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
@@ -7821,7 +7821,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>thanawia</t>
+          <t>thanawya</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
@@ -7940,7 +7940,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>thanawya</t>
+          <t>thanawia</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
@@ -8059,14 +8059,14 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>sanaweyah</t>
+          <t>thanaweya</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>th</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>ah</t>
+          <t>a</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
@@ -8182,14 +8182,14 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>thanaweya</t>
+          <t>sanaweyah</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>th</t>
+          <t>s</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>ah</t>
         </is>
       </c>
       <c r="L210" t="inlineStr"/>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
@@ -8868,14 +8868,14 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>jamal</t>
+          <t>gamal</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>j</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
@@ -8971,14 +8971,14 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>gamal</t>
+          <t>jamal</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>j</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
@@ -9692,14 +9692,14 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>haga</t>
+          <t>7aga</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -9754,7 +9754,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
@@ -9791,14 +9791,14 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>7aga</t>
+          <t>haga</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -9952,14 +9952,30 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ص</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>ح</t>
+        </is>
+      </c>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
@@ -9973,16 +9989,36 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>saha7</t>
+          <t>saba7</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr"/>
@@ -10019,30 +10055,14 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>ص</t>
-        </is>
-      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>ح</t>
-        </is>
-      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
@@ -10056,36 +10076,16 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>sabah</t>
+          <t>saha7</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
@@ -10159,7 +10159,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>saba7</t>
+          <t>sabah</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -10720,25 +10720,13 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>ذ</t>
-        </is>
-      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>ئ</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>ب</t>
-        </is>
-      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr"/>
@@ -10753,31 +10741,15 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ze2b</t>
+          <t>deeb</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr"/>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>z</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
@@ -10815,13 +10787,25 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C287" t="inlineStr"/>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>ذ</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>ئ</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
@@ -10836,15 +10820,31 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>deeb</t>
+          <t>ze2b</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr"/>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr"/>
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
@@ -11275,7 +11275,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>sahbi</t>
+          <t>sa7by</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
@@ -11382,7 +11382,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>sa7by</t>
+          <t>sahby</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -11489,7 +11489,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>sahby</t>
+          <t>sahbi</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -12042,7 +12042,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
@@ -12055,22 +12055,22 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>ر</t>
+          <t>ا</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="I326" t="inlineStr">
-        <is>
           <t>ن</t>
         </is>
       </c>
+      <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr"/>
@@ -12083,7 +12083,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>tayran</t>
+          <t>tyaran</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -12095,29 +12095,25 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
+          <t>ya</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I327" t="inlineStr">
-        <is>
           <t>n</t>
         </is>
       </c>
+      <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr"/>
@@ -12153,7 +12149,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
@@ -12166,22 +12162,22 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
         <is>
           <t>ر</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
+      <c r="H329" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
+      <c r="I329" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr"/>
@@ -12194,7 +12190,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>tyaran</t>
+          <t>tayran</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -12206,25 +12202,29 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>ya</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
           <t>r</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
+      <c r="H330" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
+      <c r="I330" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr"/>
@@ -12771,7 +12771,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
@@ -12808,19 +12808,19 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>gheab</t>
+          <t>3'yab</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>gh</t>
+          <t>3'</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>y</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
@@ -12883,17 +12883,17 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr">
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
+      <c r="H350" t="inlineStr">
         <is>
           <t>ب</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr"/>
@@ -12907,32 +12907,36 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ghyab</t>
+          <t>8eyab</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>gh</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
           <t>y</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr">
+      <c r="G351" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
+      <c r="H351" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr"/>
@@ -13068,7 +13072,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
@@ -13081,17 +13085,17 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
           <t>ب</t>
         </is>
       </c>
+      <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr"/>
@@ -13105,36 +13109,32 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>8eyab</t>
+          <t>ghyab</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>gh</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>y</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
           <t>b</t>
         </is>
       </c>
+      <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr"/>
@@ -13171,7 +13171,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
@@ -13208,19 +13208,19 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>3'yab</t>
+          <t>gheab</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>3'</t>
+          <t>gh</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
@@ -13307,14 +13307,14 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>gheyab</t>
+          <t>3'eyab</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>gh</t>
+          <t>3'</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -13476,7 +13476,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
@@ -13513,14 +13513,14 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>3'eyab</t>
+          <t>gheyab</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>3'</t>
+          <t>gh</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
@@ -13654,32 +13654,32 @@
           <t>ف</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>ر</t>
+          <t>ا</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>ا</t>
+          <t>و</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>و</t>
+          <t>ل</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="J374" t="inlineStr">
-        <is>
           <t>ة</t>
         </is>
       </c>
+      <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr"/>
       <c r="M374" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>farwla</t>
+          <t>frawla</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -13703,30 +13703,30 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>l</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="J375" t="inlineStr">
-        <is>
           <t>a</t>
         </is>
       </c>
+      <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr"/>
       <c r="M375" t="inlineStr"/>
@@ -13761,7 +13761,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
@@ -13769,32 +13769,32 @@
           <t>ف</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr">
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr">
         <is>
           <t>ر</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr">
+      <c r="G377" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr">
+      <c r="H377" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
+      <c r="I377" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr">
+      <c r="J377" t="inlineStr">
         <is>
           <t>ة</t>
         </is>
       </c>
-      <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr"/>
       <c r="M377" t="inlineStr"/>
@@ -13806,7 +13806,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>frawla</t>
+          <t>farwla</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -13818,30 +13818,30 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
           <t>r</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr">
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="I378" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr"/>
       <c r="M378" t="inlineStr"/>
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
@@ -14389,19 +14389,19 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>veranda</t>
+          <t>faranda</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>f</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
@@ -14508,21 +14508,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>faranda</t>
+          <t>phranda</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
           <t>r</t>
@@ -14582,7 +14578,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
@@ -14627,17 +14623,21 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>phranda</t>
+          <t>varanda</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>ph</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr"/>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="F399" t="inlineStr">
         <is>
           <t>r</t>
@@ -14697,7 +14697,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
@@ -14742,7 +14742,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>varanda</t>
+          <t>veranda</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -14754,7 +14754,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
@@ -14857,14 +14857,14 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>qanon</t>
+          <t>kanon</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>k</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -14923,7 +14923,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
@@ -14964,7 +14964,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>qanun</t>
+          <t>qanon</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>o</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
@@ -15071,14 +15071,14 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>kanon</t>
+          <t>qanun</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>q</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>u</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -15137,7 +15137,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
@@ -15160,12 +15160,12 @@
           <t>و</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="I413" t="inlineStr"/>
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr"/>
@@ -15178,7 +15178,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>qanoon</t>
+          <t>qanuun</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -15200,15 +15200,19 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>oo</t>
+          <t>u</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
           <t>n</t>
         </is>
       </c>
-      <c r="I414" t="inlineStr"/>
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr"/>
@@ -15244,7 +15248,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
@@ -15285,14 +15289,14 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>kanoon</t>
+          <t>qanoon</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>q</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -15351,7 +15355,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
@@ -15374,12 +15378,12 @@
           <t>و</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr"/>
-      <c r="I419" t="inlineStr">
+      <c r="H419" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
+      <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr"/>
@@ -15392,14 +15396,14 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>qanuun</t>
+          <t>kanoon</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>k</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -15414,19 +15418,15 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>oo</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="I420" t="inlineStr">
-        <is>
           <t>n</t>
         </is>
       </c>
+      <c r="I420" t="inlineStr"/>
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
@@ -15577,27 +15577,27 @@
           <t>ب</t>
         </is>
       </c>
-      <c r="E425" t="inlineStr"/>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>ت</t>
+        </is>
+      </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>ت</t>
+          <t>ق</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>ق</t>
+          <t>و</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="I425" t="inlineStr">
-        <is>
           <t>ل</t>
         </is>
       </c>
+      <c r="I425" t="inlineStr"/>
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr"/>
@@ -15610,7 +15610,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>bet2ol</t>
+          <t>bt2oul</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -15622,29 +15622,25 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>t</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>o</t>
-        </is>
-      </c>
-      <c r="I426" t="inlineStr">
-        <is>
           <t>l</t>
         </is>
       </c>
+      <c r="I426" t="inlineStr"/>
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr"/>
@@ -15680,7 +15676,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
@@ -15688,27 +15684,27 @@
           <t>ب</t>
         </is>
       </c>
-      <c r="E428" t="inlineStr">
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
         <is>
           <t>ت</t>
         </is>
       </c>
-      <c r="F428" t="inlineStr">
+      <c r="G428" t="inlineStr">
         <is>
           <t>ق</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr">
+      <c r="H428" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr">
+      <c r="I428" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="I428" t="inlineStr"/>
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr"/>
@@ -15721,7 +15717,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>bt2oul</t>
+          <t>bet2ol</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -15733,25 +15729,29 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
           <t>t</t>
         </is>
       </c>
-      <c r="F429" t="inlineStr">
+      <c r="G429" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>ou</t>
-        </is>
-      </c>
       <c r="H429" t="inlineStr">
         <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="I429" t="inlineStr"/>
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr"/>
@@ -16116,7 +16116,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
@@ -16157,7 +16157,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>bet2ool</t>
+          <t>betqool</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>q</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -16227,7 +16227,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
@@ -16268,7 +16268,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>betqool</t>
+          <t>bet2ool</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -16290,7 +16290,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
@@ -16445,17 +16445,17 @@
           <t>ك</t>
         </is>
       </c>
-      <c r="E449" t="inlineStr">
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
         <is>
           <t>ت</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr">
+      <c r="G449" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr">
         <is>
           <t>ب</t>
@@ -16474,7 +16474,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>ktaab</t>
+          <t>kitab</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -16486,12 +16486,12 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
           <t>t</t>
-        </is>
-      </c>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
@@ -16540,7 +16540,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
@@ -16577,7 +16577,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>kitab</t>
+          <t>ketab</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -16643,7 +16643,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
@@ -16651,17 +16651,17 @@
           <t>ك</t>
         </is>
       </c>
-      <c r="E455" t="inlineStr"/>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>ت</t>
+        </is>
+      </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>ت</t>
-        </is>
-      </c>
-      <c r="G455" t="inlineStr">
-        <is>
           <t>ا</t>
         </is>
       </c>
+      <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr">
         <is>
           <t>ب</t>
@@ -16680,7 +16680,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>ketab</t>
+          <t>ktaab</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -16692,12 +16692,12 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>t</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
@@ -17154,7 +17154,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
@@ -17195,7 +17195,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>gnena</t>
+          <t>gnina</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
@@ -17302,7 +17302,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>gnina</t>
+          <t>gnena</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -17368,7 +17368,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
@@ -17409,7 +17409,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>gneena</t>
+          <t>gnenaa</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -17426,7 +17426,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>ee</t>
+          <t>e</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
@@ -17439,7 +17439,11 @@
           <t>a</t>
         </is>
       </c>
-      <c r="I477" t="inlineStr"/>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr"/>
       <c r="L477" t="inlineStr"/>
@@ -17475,7 +17479,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
@@ -17516,7 +17520,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>gnenaa</t>
+          <t>gneena</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -17533,7 +17537,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>ee</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
@@ -17546,11 +17550,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="I480" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="I480" t="inlineStr"/>
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr"/>
@@ -17586,7 +17586,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
@@ -17627,7 +17627,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>genina</t>
+          <t>genena</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -17697,7 +17697,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr">
@@ -17738,7 +17738,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>genena</t>
+          <t>genina</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
@@ -18309,7 +18309,7 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J501" t="inlineStr"/>
@@ -18393,7 +18393,7 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -18428,7 +18428,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>gnenat ward</t>
+          <t>gnenet ward</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
@@ -18455,12 +18455,12 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>et</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J504" t="inlineStr"/>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
@@ -18579,7 +18579,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>gnenet ward</t>
+          <t>gnenat ward</t>
         </is>
       </c>
       <c r="B507" t="inlineStr"/>
@@ -18606,12 +18606,12 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>et</t>
+          <t>at</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J507" t="inlineStr"/>
@@ -18696,7 +18696,7 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
@@ -18767,7 +18767,7 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
@@ -18824,7 +18824,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr">
@@ -18832,42 +18832,42 @@
           <t>ج</t>
         </is>
       </c>
-      <c r="E512" t="inlineStr"/>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
       <c r="F512" t="inlineStr">
         <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="G512" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>ن</t>
+          <t>ة</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>ة</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t> </t>
+          <t>ا</t>
         </is>
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="L512" t="inlineStr">
-        <is>
           <t>ل</t>
         </is>
       </c>
+      <c r="L512" t="inlineStr"/>
       <c r="M512" t="inlineStr">
         <is>
           <t>و</t>
@@ -18889,7 +18889,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>genent elward</t>
+          <t>gnent el ward</t>
         </is>
       </c>
       <c r="B513" t="inlineStr"/>
@@ -18901,42 +18901,42 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
           <t>e</t>
         </is>
       </c>
-      <c r="F513" t="inlineStr">
+      <c r="G513" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="G513" t="inlineStr">
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="I513" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="J513" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>l</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>l</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M513" t="inlineStr">
@@ -19017,7 +19017,7 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
@@ -19052,7 +19052,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>gnent el ward</t>
+          <t>gnenet l ward</t>
         </is>
       </c>
       <c r="B516" t="inlineStr"/>
@@ -19079,19 +19079,15 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>et</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J516" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
           <t>l</t>
@@ -19099,7 +19095,7 @@
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M516" t="inlineStr">
@@ -19150,7 +19146,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C518" t="inlineStr"/>
       <c r="D518" t="inlineStr">
@@ -19158,42 +19154,42 @@
           <t>ج</t>
         </is>
       </c>
-      <c r="E518" t="inlineStr">
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="F518" t="inlineStr">
+      <c r="G518" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="G518" t="inlineStr">
+      <c r="H518" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="H518" t="inlineStr">
+      <c r="I518" t="inlineStr">
         <is>
           <t>ة</t>
         </is>
       </c>
-      <c r="I518" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="J518" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr">
+      <c r="L518" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="L518" t="inlineStr"/>
       <c r="M518" t="inlineStr">
         <is>
           <t>و</t>
@@ -19215,7 +19211,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>gnenet l ward</t>
+          <t>genent elward</t>
         </is>
       </c>
       <c r="B519" t="inlineStr"/>
@@ -19227,38 +19223,42 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
           <t>n</t>
         </is>
       </c>
-      <c r="F519" t="inlineStr">
+      <c r="G519" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="G519" t="inlineStr">
+      <c r="H519" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="H519" t="inlineStr">
-        <is>
-          <t>et</t>
-        </is>
-      </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J519" t="inlineStr"/>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="K519" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
           <t>l</t>
-        </is>
-      </c>
-      <c r="L519" t="inlineStr">
-        <is>
-          <t> </t>
         </is>
       </c>
       <c r="M519" t="inlineStr">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
@@ -19411,7 +19411,7 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="M522" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="N522" t="inlineStr">
@@ -19484,64 +19484,64 @@
           <t>ج</t>
         </is>
       </c>
-      <c r="E524" t="inlineStr"/>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
       <c r="F524" t="inlineStr">
         <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>ن</t>
+          <t>ة</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>ة</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t> </t>
+          <t>ا</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="L524" t="inlineStr">
-        <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="M524" t="inlineStr"/>
-      <c r="N524" t="inlineStr">
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="O524" t="inlineStr"/>
+      <c r="N524" t="inlineStr"/>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
       <c r="P524" t="inlineStr">
         <is>
-          <t>ر</t>
-        </is>
-      </c>
-      <c r="Q524" t="inlineStr">
-        <is>
           <t>د</t>
         </is>
       </c>
+      <c r="Q524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>genent el ward</t>
+          <t>gnenet el ward</t>
         </is>
       </c>
       <c r="B525" t="inlineStr"/>
@@ -19553,69 +19553,65 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
           <t>e</t>
         </is>
       </c>
-      <c r="F525" t="inlineStr">
+      <c r="G525" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="G525" t="inlineStr">
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>et</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="I525" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="J525" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>l</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>l</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M525" t="inlineStr">
         <is>
-          <t> </t>
+          <t>w</t>
         </is>
       </c>
       <c r="N525" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>a</t>
         </is>
       </c>
       <c r="O525" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>r</t>
         </is>
       </c>
       <c r="P525" t="inlineStr">
         <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="Q525" t="inlineStr">
-        <is>
           <t>d</t>
         </is>
       </c>
+      <c r="Q525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr"/>
@@ -19674,7 +19670,7 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
@@ -19708,7 +19704,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>geninet elward</t>
+          <t>genenat alward</t>
         </is>
       </c>
       <c r="B528" t="inlineStr"/>
@@ -19730,7 +19726,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -19740,17 +19736,17 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>et</t>
+          <t>at</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -19814,42 +19810,42 @@
           <t>ج</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr">
+      <c r="E530" t="inlineStr"/>
+      <c r="F530" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr">
+      <c r="G530" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr">
+      <c r="H530" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="H530" t="inlineStr">
+      <c r="I530" t="inlineStr">
         <is>
           <t>ة</t>
         </is>
       </c>
-      <c r="I530" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="J530" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr">
+      <c r="L530" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="L530" t="inlineStr"/>
       <c r="M530" t="inlineStr">
         <is>
           <t>و</t>
@@ -19871,7 +19867,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>gnenet el ward</t>
+          <t>geninet elward</t>
         </is>
       </c>
       <c r="B531" t="inlineStr"/>
@@ -19883,42 +19879,42 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
           <t>n</t>
         </is>
       </c>
-      <c r="F531" t="inlineStr">
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>et</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="H531" t="inlineStr">
-        <is>
-          <t>et</t>
-        </is>
-      </c>
-      <c r="I531" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J531" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="K531" t="inlineStr">
+      <c r="L531" t="inlineStr">
         <is>
           <t>l</t>
-        </is>
-      </c>
-      <c r="L531" t="inlineStr">
-        <is>
-          <t> </t>
         </is>
       </c>
       <c r="M531" t="inlineStr">
@@ -19977,42 +19973,42 @@
           <t>ج</t>
         </is>
       </c>
-      <c r="E533" t="inlineStr">
+      <c r="E533" t="inlineStr"/>
+      <c r="F533" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="F533" t="inlineStr">
+      <c r="G533" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="G533" t="inlineStr">
+      <c r="H533" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="H533" t="inlineStr">
+      <c r="I533" t="inlineStr">
         <is>
           <t>ة</t>
         </is>
       </c>
-      <c r="I533" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="J533" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr">
+      <c r="L533" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="L533" t="inlineStr"/>
       <c r="M533" t="inlineStr">
         <is>
           <t>و</t>
@@ -20034,7 +20030,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>gnenat el ward</t>
+          <t>genenet elward</t>
         </is>
       </c>
       <c r="B534" t="inlineStr"/>
@@ -20046,42 +20042,42 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
           <t>n</t>
         </is>
       </c>
-      <c r="F534" t="inlineStr">
+      <c r="G534" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="G534" t="inlineStr">
+      <c r="H534" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr">
-        <is>
-          <t>at</t>
-        </is>
-      </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t> </t>
+          <t>et</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
           <t>e</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr">
+      <c r="L534" t="inlineStr">
         <is>
           <t>l</t>
-        </is>
-      </c>
-      <c r="L534" t="inlineStr">
-        <is>
-          <t> </t>
         </is>
       </c>
       <c r="M534" t="inlineStr">
@@ -20140,42 +20136,42 @@
           <t>ج</t>
         </is>
       </c>
-      <c r="E536" t="inlineStr"/>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
       <c r="F536" t="inlineStr">
         <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="G536" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>ن</t>
+          <t>ة</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>ة</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t> </t>
+          <t>ا</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="L536" t="inlineStr">
-        <is>
           <t>ل</t>
         </is>
       </c>
+      <c r="L536" t="inlineStr"/>
       <c r="M536" t="inlineStr">
         <is>
           <t>و</t>
@@ -20197,7 +20193,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>genenat alward</t>
+          <t>gnenat el ward</t>
         </is>
       </c>
       <c r="B537" t="inlineStr"/>
@@ -20209,42 +20205,42 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
           <t>e</t>
         </is>
       </c>
-      <c r="F537" t="inlineStr">
+      <c r="G537" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="G537" t="inlineStr">
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="H537" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="I537" t="inlineStr">
-        <is>
-          <t>at</t>
-        </is>
-      </c>
-      <c r="J537" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>l</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>l</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M537" t="inlineStr">
@@ -20326,7 +20322,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K539" t="inlineStr">
@@ -20339,28 +20335,28 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="M539" t="inlineStr">
+      <c r="M539" t="inlineStr"/>
+      <c r="N539" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="N539" t="inlineStr"/>
-      <c r="O539" t="inlineStr">
+      <c r="O539" t="inlineStr"/>
+      <c r="P539" t="inlineStr">
         <is>
           <t>ر</t>
         </is>
       </c>
-      <c r="P539" t="inlineStr">
+      <c r="Q539" t="inlineStr">
         <is>
           <t>د</t>
         </is>
       </c>
-      <c r="Q539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>genenet elward</t>
+          <t>genent el ward</t>
         </is>
       </c>
       <c r="B540" t="inlineStr"/>
@@ -20392,12 +20388,12 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>et</t>
+          <t>t</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
@@ -20412,25 +20408,29 @@
       </c>
       <c r="M540" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
           <t>w</t>
         </is>
       </c>
-      <c r="N540" t="inlineStr">
+      <c r="O540" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="O540" t="inlineStr">
+      <c r="P540" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="P540" t="inlineStr">
+      <c r="Q540" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="Q540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr"/>
@@ -20458,7 +20458,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K542" t="inlineStr">
@@ -20502,28 +20502,28 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="M542" t="inlineStr"/>
-      <c r="N542" t="inlineStr">
+      <c r="M542" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="O542" t="inlineStr"/>
+      <c r="N542" t="inlineStr"/>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
       <c r="P542" t="inlineStr">
         <is>
-          <t>ر</t>
-        </is>
-      </c>
-      <c r="Q542" t="inlineStr">
-        <is>
           <t>د</t>
         </is>
       </c>
+      <c r="Q542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>genenet el ward</t>
+          <t>geneenet elward</t>
         </is>
       </c>
       <c r="B543" t="inlineStr"/>
@@ -20545,29 +20545,29 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
+          <t>ee</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>et</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
           <t>e</t>
         </is>
       </c>
-      <c r="H543" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="I543" t="inlineStr">
-        <is>
-          <t>et</t>
-        </is>
-      </c>
-      <c r="J543" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K543" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>l</t>
@@ -20575,29 +20575,25 @@
       </c>
       <c r="M543" t="inlineStr">
         <is>
-          <t> </t>
+          <t>w</t>
         </is>
       </c>
       <c r="N543" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>a</t>
         </is>
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>r</t>
         </is>
       </c>
       <c r="P543" t="inlineStr">
         <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="Q543" t="inlineStr">
-        <is>
           <t>d</t>
         </is>
       </c>
+      <c r="Q543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr"/>
@@ -20655,7 +20651,7 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
@@ -20690,7 +20686,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>gneenet el ward</t>
+          <t>gneenat el ward</t>
         </is>
       </c>
       <c r="B546" t="inlineStr"/>
@@ -20717,12 +20713,12 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>et</t>
+          <t>at</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
@@ -20737,7 +20733,7 @@
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M546" t="inlineStr">
@@ -20788,7 +20784,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
@@ -20819,7 +20815,7 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
@@ -20832,28 +20828,28 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="M548" t="inlineStr">
+      <c r="M548" t="inlineStr"/>
+      <c r="N548" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="N548" t="inlineStr"/>
-      <c r="O548" t="inlineStr">
+      <c r="O548" t="inlineStr"/>
+      <c r="P548" t="inlineStr">
         <is>
           <t>ر</t>
         </is>
       </c>
-      <c r="P548" t="inlineStr">
+      <c r="Q548" t="inlineStr">
         <is>
           <t>د</t>
         </is>
       </c>
-      <c r="Q548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>geneenat alward</t>
+          <t>genenet el ward</t>
         </is>
       </c>
       <c r="B549" t="inlineStr"/>
@@ -20875,7 +20871,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>ee</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -20885,45 +20881,49 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>et</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K549" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="L549" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="M549" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="N549" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="O549" t="inlineStr">
+      <c r="P549" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="P549" t="inlineStr">
+      <c r="Q549" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="Q549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr"/>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
@@ -21016,7 +21016,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>geneenet elward</t>
+          <t>geneenat alward</t>
         </is>
       </c>
       <c r="B552" t="inlineStr"/>
@@ -21048,17 +21048,17 @@
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>et</t>
+          <t>at</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
@@ -21179,7 +21179,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>gneenat el ward</t>
+          <t>gneenet el ward</t>
         </is>
       </c>
       <c r="B555" t="inlineStr"/>
@@ -21206,12 +21206,12 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>et</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
@@ -21226,7 +21226,7 @@
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M555" t="inlineStr">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K557" t="inlineStr">
@@ -21379,7 +21379,7 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K558" t="inlineStr">
@@ -21394,7 +21394,7 @@
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="N558" t="inlineStr">
@@ -21666,22 +21666,22 @@
           <t>أ</t>
         </is>
       </c>
-      <c r="E566" t="inlineStr"/>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>ل</t>
+          <t>و</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="H566" t="inlineStr">
-        <is>
           <t>ا</t>
         </is>
       </c>
+      <c r="H566" t="inlineStr"/>
       <c r="I566" t="inlineStr">
         <is>
           <t>ن</t>
@@ -21699,29 +21699,29 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2alwan</t>
+          <t>alwaan</t>
         </is>
       </c>
       <c r="B567" t="inlineStr"/>
       <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
           <t>a</t>
-        </is>
-      </c>
-      <c r="F567" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>w</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -21777,22 +21777,22 @@
           <t>أ</t>
         </is>
       </c>
-      <c r="E569" t="inlineStr">
+      <c r="E569" t="inlineStr"/>
+      <c r="F569" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="F569" t="inlineStr">
+      <c r="G569" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="G569" t="inlineStr">
+      <c r="H569" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="H569" t="inlineStr"/>
       <c r="I569" t="inlineStr">
         <is>
           <t>ن</t>
@@ -21810,29 +21810,29 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>alwaan</t>
+          <t>2alwan</t>
         </is>
       </c>
       <c r="B570" t="inlineStr"/>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E570" t="inlineStr">
+      <c r="F570" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="F570" t="inlineStr">
+      <c r="G570" t="inlineStr">
         <is>
           <t>w</t>
-        </is>
-      </c>
-      <c r="G570" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -21987,7 +21987,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr">
@@ -22028,7 +22028,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>m3roof</t>
+          <t>ma'rof</t>
         </is>
       </c>
       <c r="B576" t="inlineStr"/>
@@ -22040,7 +22040,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>a'</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>oo</t>
+          <t>o</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -22094,7 +22094,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
@@ -22102,27 +22102,27 @@
           <t>م</t>
         </is>
       </c>
-      <c r="E578" t="inlineStr"/>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>ع</t>
+        </is>
+      </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>ع</t>
+          <t>ر</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>ر</t>
+          <t>و</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="I578" t="inlineStr">
-        <is>
           <t>ف</t>
         </is>
       </c>
+      <c r="I578" t="inlineStr"/>
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr"/>
       <c r="L578" t="inlineStr"/>
@@ -22135,7 +22135,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>ma3rof</t>
+          <t>m3roof</t>
         </is>
       </c>
       <c r="B579" t="inlineStr"/>
@@ -22147,29 +22147,25 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>r</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>oo</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>o</t>
-        </is>
-      </c>
-      <c r="I579" t="inlineStr">
-        <is>
           <t>f</t>
         </is>
       </c>
+      <c r="I579" t="inlineStr"/>
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr"/>
       <c r="L579" t="inlineStr"/>
@@ -22213,12 +22209,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="E581" t="inlineStr">
+      <c r="E581" t="inlineStr"/>
+      <c r="F581" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
-      <c r="F581" t="inlineStr"/>
       <c r="G581" t="inlineStr">
         <is>
           <t>ر</t>
@@ -22246,7 +22242,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>m3arof</t>
+          <t>ma3ruf</t>
         </is>
       </c>
       <c r="B582" t="inlineStr"/>
@@ -22258,14 +22254,14 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F582" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
       <c r="G582" t="inlineStr">
         <is>
           <t>r</t>
@@ -22273,7 +22269,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>u</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -22316,7 +22312,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
@@ -22357,7 +22353,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>ma3ruf</t>
+          <t>ma3rof</t>
         </is>
       </c>
       <c r="B585" t="inlineStr"/>
@@ -22384,7 +22380,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>o</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -22440,22 +22436,22 @@
           <t>ع</t>
         </is>
       </c>
-      <c r="F587" t="inlineStr">
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr">
         <is>
           <t>ر</t>
         </is>
       </c>
-      <c r="G587" t="inlineStr">
+      <c r="H587" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="H587" t="inlineStr">
+      <c r="I587" t="inlineStr">
         <is>
           <t>ف</t>
         </is>
       </c>
-      <c r="I587" t="inlineStr"/>
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr"/>
       <c r="L587" t="inlineStr"/>
@@ -22468,7 +22464,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>ma'rof</t>
+          <t>m3arof</t>
         </is>
       </c>
       <c r="B588" t="inlineStr"/>
@@ -22480,25 +22476,29 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>a'</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
           <t>r</t>
         </is>
       </c>
-      <c r="G588" t="inlineStr">
+      <c r="H588" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="H588" t="inlineStr">
+      <c r="I588" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="I588" t="inlineStr"/>
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr"/>
       <c r="L588" t="inlineStr"/>
@@ -22534,7 +22534,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
@@ -22575,7 +22575,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>ma3rouf</t>
+          <t>ma3roof</t>
         </is>
       </c>
       <c r="B591" t="inlineStr"/>
@@ -22602,7 +22602,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>oo</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -22645,7 +22645,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
@@ -22686,7 +22686,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>ma3roof</t>
+          <t>ma3rouf</t>
         </is>
       </c>
       <c r="B594" t="inlineStr"/>
@@ -22713,7 +22713,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>oo</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -22764,17 +22764,17 @@
           <t>ن</t>
         </is>
       </c>
-      <c r="E596" t="inlineStr"/>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="G596" t="inlineStr">
-        <is>
           <t>و</t>
         </is>
       </c>
+      <c r="G596" t="inlineStr"/>
       <c r="H596" t="inlineStr"/>
       <c r="I596" t="inlineStr"/>
       <c r="J596" t="inlineStr"/>
@@ -22789,7 +22789,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>nomw</t>
+          <t>nmoo</t>
         </is>
       </c>
       <c r="B597" t="inlineStr"/>
@@ -22801,19 +22801,15 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="G597" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
+          <t>oo</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr"/>
       <c r="H597" t="inlineStr"/>
       <c r="I597" t="inlineStr"/>
       <c r="J597" t="inlineStr"/>
@@ -22946,7 +22942,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
@@ -22979,7 +22975,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>nemw</t>
+          <t>nomo</t>
         </is>
       </c>
       <c r="B603" t="inlineStr"/>
@@ -22991,7 +22987,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
@@ -23001,7 +22997,7 @@
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>o</t>
         </is>
       </c>
       <c r="H603" t="inlineStr"/>
@@ -23041,7 +23037,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
@@ -23049,17 +23045,17 @@
           <t>ن</t>
         </is>
       </c>
-      <c r="E605" t="inlineStr">
+      <c r="E605" t="inlineStr"/>
+      <c r="F605" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
-      <c r="F605" t="inlineStr">
+      <c r="G605" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="G605" t="inlineStr"/>
       <c r="H605" t="inlineStr"/>
       <c r="I605" t="inlineStr"/>
       <c r="J605" t="inlineStr"/>
@@ -23074,7 +23070,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>nmoo</t>
+          <t>nomu</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
@@ -23086,15 +23082,19 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F606" t="inlineStr">
-        <is>
-          <t>oo</t>
-        </is>
-      </c>
-      <c r="G606" t="inlineStr"/>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
       <c r="H606" t="inlineStr"/>
       <c r="I606" t="inlineStr"/>
       <c r="J606" t="inlineStr"/>
@@ -23132,7 +23132,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr">
@@ -23165,7 +23165,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>nomu</t>
+          <t>nemw</t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
@@ -23177,7 +23177,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>w</t>
         </is>
       </c>
       <c r="H609" t="inlineStr"/>
@@ -23227,7 +23227,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>nomo</t>
+          <t>nomw</t>
         </is>
       </c>
       <c r="B612" t="inlineStr"/>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>w</t>
         </is>
       </c>
       <c r="H612" t="inlineStr"/>
@@ -23336,12 +23336,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="G614" t="inlineStr">
+      <c r="G614" t="inlineStr"/>
+      <c r="H614" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="H614" t="inlineStr"/>
       <c r="I614" t="inlineStr"/>
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr"/>
@@ -23355,7 +23355,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>nomou</t>
+          <t>numuw</t>
         </is>
       </c>
       <c r="B615" t="inlineStr"/>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>u</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
@@ -23377,10 +23377,14 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>ou</t>
-        </is>
-      </c>
-      <c r="H615" t="inlineStr"/>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
       <c r="I615" t="inlineStr"/>
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr"/>
@@ -23450,7 +23454,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>numuw</t>
+          <t>nemew</t>
         </is>
       </c>
       <c r="B618" t="inlineStr"/>
@@ -23462,7 +23466,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
@@ -23472,7 +23476,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -23516,7 +23520,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C620" t="inlineStr"/>
       <c r="D620" t="inlineStr">
@@ -23530,12 +23534,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="G620" t="inlineStr">
+      <c r="G620" t="inlineStr"/>
+      <c r="H620" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="H620" t="inlineStr"/>
       <c r="I620" t="inlineStr"/>
       <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr"/>
@@ -23549,7 +23553,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>nemmo</t>
+          <t>nomow</t>
         </is>
       </c>
       <c r="B621" t="inlineStr"/>
@@ -23561,12 +23565,12 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
@@ -23574,7 +23578,11 @@
           <t>o</t>
         </is>
       </c>
-      <c r="H621" t="inlineStr"/>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
       <c r="I621" t="inlineStr"/>
       <c r="J621" t="inlineStr"/>
       <c r="K621" t="inlineStr"/>
@@ -23611,7 +23619,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr">
@@ -23644,7 +23652,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>nemow</t>
+          <t>numow</t>
         </is>
       </c>
       <c r="B624" t="inlineStr"/>
@@ -23656,7 +23664,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
@@ -23724,12 +23732,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="G626" t="inlineStr"/>
-      <c r="H626" t="inlineStr">
+      <c r="G626" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
+      <c r="H626" t="inlineStr"/>
       <c r="I626" t="inlineStr"/>
       <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr"/>
@@ -23743,7 +23751,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>numow</t>
+          <t>nomou</t>
         </is>
       </c>
       <c r="B627" t="inlineStr"/>
@@ -23755,7 +23763,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
@@ -23765,14 +23773,10 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>o</t>
-        </is>
-      </c>
-      <c r="H627" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
+          <t>ou</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr"/>
       <c r="I627" t="inlineStr"/>
       <c r="J627" t="inlineStr"/>
       <c r="K627" t="inlineStr"/>
@@ -23809,7 +23813,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr">
@@ -23842,7 +23846,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>nomow</t>
+          <t>nemow</t>
         </is>
       </c>
       <c r="B630" t="inlineStr"/>
@@ -23854,7 +23858,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
@@ -23922,12 +23926,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="G632" t="inlineStr"/>
-      <c r="H632" t="inlineStr">
+      <c r="G632" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
+      <c r="H632" t="inlineStr"/>
       <c r="I632" t="inlineStr"/>
       <c r="J632" t="inlineStr"/>
       <c r="K632" t="inlineStr"/>
@@ -23941,7 +23945,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>nemew</t>
+          <t>nemmo</t>
         </is>
       </c>
       <c r="B633" t="inlineStr"/>
@@ -23958,19 +23962,15 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H633" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr"/>
       <c r="I633" t="inlineStr"/>
       <c r="J633" t="inlineStr"/>
       <c r="K633" t="inlineStr"/>
@@ -24440,7 +24440,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>waady</t>
+          <t>waadi</t>
         </is>
       </c>
       <c r="B648" t="inlineStr"/>
@@ -24467,7 +24467,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="I648" t="inlineStr"/>
@@ -24519,17 +24519,17 @@
           <t>ا</t>
         </is>
       </c>
-      <c r="F650" t="inlineStr">
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr">
         <is>
           <t>د</t>
         </is>
       </c>
-      <c r="G650" t="inlineStr">
+      <c r="H650" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="H650" t="inlineStr"/>
       <c r="I650" t="inlineStr"/>
       <c r="J650" t="inlineStr"/>
       <c r="K650" t="inlineStr"/>
@@ -24543,7 +24543,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>wadii</t>
+          <t>waady</t>
         </is>
       </c>
       <c r="B651" t="inlineStr"/>
@@ -24560,17 +24560,17 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
           <t>d</t>
         </is>
       </c>
-      <c r="G651" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="I651" t="inlineStr"/>
@@ -24622,17 +24622,17 @@
           <t>ا</t>
         </is>
       </c>
-      <c r="F653" t="inlineStr"/>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>د</t>
+        </is>
+      </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>د</t>
-        </is>
-      </c>
-      <c r="H653" t="inlineStr">
-        <is>
           <t>ي</t>
         </is>
       </c>
+      <c r="H653" t="inlineStr"/>
       <c r="I653" t="inlineStr"/>
       <c r="J653" t="inlineStr"/>
       <c r="K653" t="inlineStr"/>
@@ -24646,7 +24646,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>waadi</t>
+          <t>wadii</t>
         </is>
       </c>
       <c r="B654" t="inlineStr"/>
@@ -24663,12 +24663,12 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>i</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -24712,7 +24712,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
@@ -24745,7 +24745,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>abu</t>
+          <t>abo</t>
         </is>
       </c>
       <c r="B657" t="inlineStr"/>
@@ -24762,7 +24762,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>o</t>
         </is>
       </c>
       <c r="G657" t="inlineStr"/>
@@ -24803,7 +24803,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr">
@@ -24836,7 +24836,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>abo</t>
+          <t>abu</t>
         </is>
       </c>
       <c r="B660" t="inlineStr"/>
@@ -24853,7 +24853,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>u</t>
         </is>
       </c>
       <c r="G660" t="inlineStr"/>
@@ -25853,7 +25853,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
@@ -25898,7 +25898,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>veranda</t>
+          <t>varanda</t>
         </is>
       </c>
       <c r="B690" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
@@ -25972,7 +25972,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C692" t="inlineStr"/>
       <c r="D692" t="inlineStr">
@@ -26017,7 +26017,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>varanda</t>
+          <t>veranda</t>
         </is>
       </c>
       <c r="B693" t="inlineStr"/>
@@ -26029,7 +26029,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
